--- a/resultados/resultados_RS_cv_vs_test_.xlsx
+++ b/resultados/resultados_RS_cv_vs_test_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnatello\Documents\GitHub\etapa-analisis_pcsmote\resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos_D\etapa-analisis_pcsmote\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348B86DC-BD89-40F9-817D-15C21F2FE494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36051197-9858-4441-A27E-B87C4FB71353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$1165</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -416,9 +411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -456,9 +451,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -491,26 +486,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -543,26 +521,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -794,7 +755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
@@ -2533,7 +2494,7 @@
         <v>0.90900000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>19</v>
       </c>
@@ -6669,7 +6630,7 @@
         <v>0.89500000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>15</v>
       </c>
@@ -6710,7 +6671,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>15</v>
       </c>
@@ -6798,7 +6759,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>15</v>
       </c>
@@ -6839,7 +6800,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>19</v>
       </c>
@@ -8155,7 +8116,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>19</v>
       </c>
@@ -8202,7 +8163,7 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>19</v>
       </c>
@@ -8249,7 +8210,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>19</v>
       </c>
@@ -47235,7 +47196,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="997" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A997" s="3" t="s">
         <v>17</v>
       </c>
@@ -47278,7 +47239,7 @@
         <v>0.99099999999999999</v>
       </c>
     </row>
-    <row r="998" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A998" s="3" t="s">
         <v>16</v>
       </c>
@@ -47321,7 +47282,7 @@
         <v>0.97199999999999998</v>
       </c>
     </row>
-    <row r="999" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A999" s="3" t="s">
         <v>16</v>
       </c>
@@ -47364,7 +47325,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1000" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1000" s="3" t="s">
         <v>19</v>
       </c>
@@ -47411,7 +47372,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1001" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1001" s="3" t="s">
         <v>19</v>
       </c>
@@ -47458,7 +47419,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1002" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1002" s="3" t="s">
         <v>19</v>
       </c>
@@ -47505,7 +47466,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1003" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1003" s="3" t="s">
         <v>19</v>
       </c>
@@ -47552,7 +47513,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1004" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1004" s="3" t="s">
         <v>19</v>
       </c>
@@ -47599,7 +47560,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1005" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1005" s="3" t="s">
         <v>19</v>
       </c>
@@ -47646,7 +47607,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1006" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1006" s="3" t="s">
         <v>15</v>
       </c>
@@ -47687,7 +47648,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1007" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1007" s="3" t="s">
         <v>15</v>
       </c>
@@ -47728,7 +47689,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1008" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1008" s="3" t="s">
         <v>19</v>
       </c>
@@ -47775,7 +47736,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1009" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1009" s="3" t="s">
         <v>19</v>
       </c>
@@ -47822,7 +47783,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1010" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1010" s="3" t="s">
         <v>19</v>
       </c>
@@ -47869,7 +47830,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1011" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1011" s="3" t="s">
         <v>19</v>
       </c>
@@ -47916,7 +47877,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1012" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1012" s="3" t="s">
         <v>19</v>
       </c>
@@ -47963,7 +47924,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1013" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1013" s="3" t="s">
         <v>19</v>
       </c>
@@ -48010,7 +47971,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1014" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1014" s="3" t="s">
         <v>16</v>
       </c>
@@ -48053,7 +48014,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1015" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1015" s="3" t="s">
         <v>19</v>
       </c>
@@ -48100,7 +48061,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1016" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1016" s="3" t="s">
         <v>19</v>
       </c>
@@ -48147,7 +48108,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1017" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1017" s="3" t="s">
         <v>19</v>
       </c>
@@ -48194,7 +48155,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1018" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1018" s="3" t="s">
         <v>19</v>
       </c>
@@ -48241,7 +48202,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1019" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1019" s="3" t="s">
         <v>19</v>
       </c>
@@ -48288,7 +48249,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1020" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1020" s="3" t="s">
         <v>19</v>
       </c>
@@ -48335,7 +48296,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1021" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1021" s="3" t="s">
         <v>17</v>
       </c>
@@ -48378,7 +48339,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1022" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1022" s="3" t="s">
         <v>19</v>
       </c>
@@ -48425,7 +48386,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1023" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1023" s="3" t="s">
         <v>19</v>
       </c>
@@ -48472,7 +48433,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1024" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1024" s="3" t="s">
         <v>19</v>
       </c>
@@ -48519,7 +48480,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1025" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1025" s="3" t="s">
         <v>19</v>
       </c>
@@ -48566,7 +48527,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1026" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1026" s="3" t="s">
         <v>19</v>
       </c>
@@ -48613,7 +48574,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1027" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1027" s="3" t="s">
         <v>19</v>
       </c>
@@ -48660,7 +48621,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1028" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1028" s="3" t="s">
         <v>18</v>
       </c>
@@ -48703,7 +48664,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1029" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1029" s="3" t="s">
         <v>19</v>
       </c>
@@ -48750,7 +48711,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1030" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1030" s="3" t="s">
         <v>19</v>
       </c>
@@ -48797,7 +48758,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1031" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1031" s="3" t="s">
         <v>19</v>
       </c>
@@ -48844,7 +48805,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1032" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1032" s="3" t="s">
         <v>19</v>
       </c>
@@ -48891,7 +48852,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1033" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1033" s="3" t="s">
         <v>19</v>
       </c>
@@ -48938,7 +48899,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1034" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1034" s="3" t="s">
         <v>19</v>
       </c>
@@ -48985,7 +48946,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1035" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1035" s="3" t="s">
         <v>19</v>
       </c>
@@ -49032,7 +48993,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1036" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1036" s="3" t="s">
         <v>19</v>
       </c>
@@ -49079,7 +49040,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1037" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1037" s="3" t="s">
         <v>19</v>
       </c>
@@ -49126,7 +49087,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1038" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1038" s="3" t="s">
         <v>19</v>
       </c>
@@ -49173,7 +49134,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1039" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1039" s="3" t="s">
         <v>19</v>
       </c>
@@ -49220,7 +49181,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1040" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1040" s="3" t="s">
         <v>19</v>
       </c>
@@ -49267,7 +49228,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1041" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1041" s="3" t="s">
         <v>19</v>
       </c>
@@ -49314,7 +49275,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1042" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1042" s="3" t="s">
         <v>19</v>
       </c>
@@ -49361,7 +49322,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1043" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1043" s="3" t="s">
         <v>19</v>
       </c>
@@ -49408,7 +49369,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1044" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1044" s="3" t="s">
         <v>19</v>
       </c>
@@ -49455,7 +49416,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1045" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1045" s="3" t="s">
         <v>19</v>
       </c>
@@ -49502,7 +49463,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1046" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1046" s="3" t="s">
         <v>19</v>
       </c>
@@ -49549,7 +49510,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1047" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1047" s="3" t="s">
         <v>19</v>
       </c>
@@ -49596,7 +49557,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1048" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1048" s="3" t="s">
         <v>19</v>
       </c>
@@ -49643,7 +49604,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1049" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1049" s="3" t="s">
         <v>19</v>
       </c>
@@ -49690,7 +49651,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1050" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1050" s="3" t="s">
         <v>19</v>
       </c>
@@ -49737,7 +49698,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1051" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1051" s="3" t="s">
         <v>19</v>
       </c>
@@ -49784,7 +49745,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1052" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1052" s="3" t="s">
         <v>19</v>
       </c>
@@ -49831,7 +49792,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1053" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1053" s="3" t="s">
         <v>19</v>
       </c>
@@ -49878,7 +49839,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1054" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1054" s="3" t="s">
         <v>19</v>
       </c>
@@ -49925,7 +49886,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1055" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1055" s="3" t="s">
         <v>19</v>
       </c>
@@ -49972,7 +49933,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1056" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1056" s="3" t="s">
         <v>19</v>
       </c>
@@ -50019,7 +49980,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1057" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1057" s="3" t="s">
         <v>19</v>
       </c>
@@ -50066,7 +50027,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1058" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1058" s="3" t="s">
         <v>19</v>
       </c>
@@ -50113,7 +50074,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1059" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1059" s="3" t="s">
         <v>19</v>
       </c>
@@ -50160,7 +50121,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1060" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1060" s="3" t="s">
         <v>19</v>
       </c>
@@ -50207,7 +50168,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1061" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1061" s="3" t="s">
         <v>19</v>
       </c>
@@ -50254,7 +50215,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1062" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1062" s="3" t="s">
         <v>19</v>
       </c>
@@ -50301,7 +50262,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1063" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1063" s="3" t="s">
         <v>19</v>
       </c>
@@ -50348,7 +50309,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1064" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1064" s="3" t="s">
         <v>19</v>
       </c>
@@ -50395,7 +50356,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1065" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1065" s="3" t="s">
         <v>19</v>
       </c>
@@ -50442,7 +50403,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1066" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1066" s="3" t="s">
         <v>19</v>
       </c>
@@ -50489,7 +50450,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1067" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1067" s="3" t="s">
         <v>19</v>
       </c>
@@ -50536,7 +50497,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1068" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1068" s="3" t="s">
         <v>19</v>
       </c>
@@ -50583,7 +50544,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1069" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1069" s="3" t="s">
         <v>19</v>
       </c>
@@ -50630,7 +50591,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1070" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1070" s="3" t="s">
         <v>19</v>
       </c>
@@ -50677,7 +50638,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1071" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1071" s="3" t="s">
         <v>19</v>
       </c>
@@ -50724,7 +50685,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1072" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1072" s="3" t="s">
         <v>19</v>
       </c>
@@ -50771,7 +50732,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1073" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1073" s="3" t="s">
         <v>19</v>
       </c>
@@ -50818,7 +50779,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1074" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1074" s="3" t="s">
         <v>19</v>
       </c>
@@ -50865,7 +50826,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1075" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1075" s="3" t="s">
         <v>19</v>
       </c>
@@ -50912,7 +50873,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1076" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1076" s="3" t="s">
         <v>19</v>
       </c>
@@ -50959,7 +50920,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1077" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1077" s="3" t="s">
         <v>19</v>
       </c>
@@ -51006,7 +50967,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1078" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1078" s="3" t="s">
         <v>19</v>
       </c>
@@ -51053,7 +51014,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1079" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1079" s="3" t="s">
         <v>19</v>
       </c>
@@ -51100,7 +51061,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1080" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1080" s="3" t="s">
         <v>19</v>
       </c>
@@ -51147,7 +51108,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1081" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1081" s="3" t="s">
         <v>19</v>
       </c>
@@ -51194,7 +51155,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1082" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1082" s="3" t="s">
         <v>19</v>
       </c>
@@ -51241,7 +51202,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1083" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1083" s="3" t="s">
         <v>19</v>
       </c>
@@ -51288,7 +51249,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1084" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1084" s="3" t="s">
         <v>19</v>
       </c>
@@ -51335,7 +51296,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1085" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1085" s="3" t="s">
         <v>19</v>
       </c>
@@ -51382,7 +51343,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1086" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1086" s="3" t="s">
         <v>19</v>
       </c>
@@ -51429,7 +51390,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1087" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1087" s="3" t="s">
         <v>19</v>
       </c>
@@ -51476,7 +51437,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1088" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1088" s="3" t="s">
         <v>19</v>
       </c>
@@ -51523,7 +51484,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1089" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1089" s="3" t="s">
         <v>19</v>
       </c>
@@ -51570,7 +51531,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1090" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1090" s="3" t="s">
         <v>19</v>
       </c>
@@ -51617,7 +51578,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1091" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1091" s="3" t="s">
         <v>19</v>
       </c>
@@ -51664,7 +51625,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1092" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1092" s="3" t="s">
         <v>19</v>
       </c>
@@ -51711,7 +51672,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1093" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1093" s="3" t="s">
         <v>19</v>
       </c>
@@ -51758,7 +51719,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1094" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1094" s="3" t="s">
         <v>19</v>
       </c>
@@ -51805,7 +51766,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1095" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1095" s="3" t="s">
         <v>19</v>
       </c>
@@ -51852,7 +51813,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1096" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1096" s="3" t="s">
         <v>19</v>
       </c>
@@ -51899,7 +51860,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1097" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1097" s="3" t="s">
         <v>19</v>
       </c>
@@ -51946,7 +51907,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1098" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1098" s="3" t="s">
         <v>19</v>
       </c>
@@ -51993,7 +51954,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1099" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1099" s="3" t="s">
         <v>19</v>
       </c>
@@ -52040,7 +52001,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1100" s="3" t="s">
         <v>19</v>
       </c>
@@ -52087,7 +52048,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1101" s="3" t="s">
         <v>19</v>
       </c>
@@ -52134,7 +52095,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1102" s="3" t="s">
         <v>19</v>
       </c>
@@ -52181,7 +52142,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1103" s="3" t="s">
         <v>19</v>
       </c>
@@ -52228,7 +52189,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1104" s="3" t="s">
         <v>19</v>
       </c>
@@ -52275,7 +52236,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1105" s="3" t="s">
         <v>19</v>
       </c>
@@ -52322,7 +52283,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1106" s="3" t="s">
         <v>19</v>
       </c>
@@ -52369,7 +52330,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1107" s="3" t="s">
         <v>19</v>
       </c>
@@ -52416,7 +52377,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1108" s="3" t="s">
         <v>19</v>
       </c>
@@ -52463,7 +52424,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1109" s="3" t="s">
         <v>19</v>
       </c>
@@ -52510,7 +52471,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1110" s="3" t="s">
         <v>19</v>
       </c>
@@ -52557,7 +52518,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1111" s="3" t="s">
         <v>19</v>
       </c>
@@ -52604,7 +52565,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1112" s="3" t="s">
         <v>19</v>
       </c>
@@ -52651,7 +52612,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1113" s="3" t="s">
         <v>19</v>
       </c>
@@ -52698,7 +52659,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1114" s="3" t="s">
         <v>19</v>
       </c>
@@ -52745,7 +52706,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1115" s="3" t="s">
         <v>19</v>
       </c>
@@ -52792,7 +52753,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1116" s="3" t="s">
         <v>19</v>
       </c>
@@ -52839,7 +52800,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1117" s="3" t="s">
         <v>19</v>
       </c>
@@ -52886,7 +52847,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1118" s="3" t="s">
         <v>19</v>
       </c>
@@ -52933,7 +52894,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1119" s="3" t="s">
         <v>19</v>
       </c>
@@ -52980,7 +52941,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1120" s="3" t="s">
         <v>19</v>
       </c>
@@ -53027,7 +52988,7 @@
         <v>0.97099999999999997</v>
       </c>
     </row>
-    <row r="1121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1121" s="3" t="s">
         <v>18</v>
       </c>
@@ -53070,7 +53031,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1122" s="3" t="s">
         <v>17</v>
       </c>
@@ -53113,7 +53074,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1123" s="3" t="s">
         <v>18</v>
       </c>
@@ -53156,7 +53117,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1124" s="3" t="s">
         <v>19</v>
       </c>
@@ -53203,7 +53164,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1125" s="3" t="s">
         <v>19</v>
       </c>
@@ -53250,7 +53211,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1126" s="3" t="s">
         <v>19</v>
       </c>
@@ -53297,7 +53258,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1127" s="3" t="s">
         <v>19</v>
       </c>
@@ -53344,7 +53305,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1128" s="3" t="s">
         <v>19</v>
       </c>
@@ -53391,7 +53352,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1129" s="3" t="s">
         <v>19</v>
       </c>
@@ -53438,7 +53399,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1130" s="3" t="s">
         <v>19</v>
       </c>
@@ -53485,7 +53446,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1131" s="3" t="s">
         <v>19</v>
       </c>
@@ -53532,7 +53493,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1132" s="3" t="s">
         <v>19</v>
       </c>
@@ -53579,7 +53540,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1133" s="3" t="s">
         <v>19</v>
       </c>
@@ -53626,7 +53587,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1134" s="3" t="s">
         <v>19</v>
       </c>
@@ -53673,7 +53634,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1135" s="3" t="s">
         <v>19</v>
       </c>
@@ -53720,7 +53681,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1136" s="3" t="s">
         <v>19</v>
       </c>
@@ -53767,7 +53728,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1137" s="3" t="s">
         <v>19</v>
       </c>
@@ -53814,7 +53775,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1138" s="3" t="s">
         <v>19</v>
       </c>
@@ -53861,7 +53822,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1139" s="3" t="s">
         <v>19</v>
       </c>
@@ -53908,7 +53869,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1140" s="3" t="s">
         <v>19</v>
       </c>
@@ -53955,7 +53916,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1141" s="3" t="s">
         <v>19</v>
       </c>
@@ -54002,7 +53963,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1142" s="3" t="s">
         <v>19</v>
       </c>
@@ -54049,7 +54010,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1143" s="3" t="s">
         <v>19</v>
       </c>
@@ -54096,7 +54057,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1144" s="3" t="s">
         <v>19</v>
       </c>
@@ -54143,7 +54104,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1145" s="3" t="s">
         <v>19</v>
       </c>
@@ -54190,7 +54151,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1146" s="3" t="s">
         <v>19</v>
       </c>
@@ -54237,7 +54198,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1147" s="3" t="s">
         <v>19</v>
       </c>
@@ -54284,7 +54245,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1148" s="3" t="s">
         <v>19</v>
       </c>
@@ -54331,7 +54292,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1149" s="3" t="s">
         <v>19</v>
       </c>
@@ -54378,7 +54339,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1150" s="3" t="s">
         <v>19</v>
       </c>
@@ -54425,7 +54386,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1151" s="3" t="s">
         <v>19</v>
       </c>
@@ -54472,7 +54433,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1152" s="3" t="s">
         <v>19</v>
       </c>
@@ -54519,7 +54480,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1153" s="3" t="s">
         <v>19</v>
       </c>
@@ -54566,7 +54527,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1154" s="3" t="s">
         <v>19</v>
       </c>
@@ -54613,7 +54574,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1155" s="3" t="s">
         <v>19</v>
       </c>
@@ -54660,7 +54621,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1156" s="3" t="s">
         <v>19</v>
       </c>
@@ -54707,7 +54668,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1157" s="3" t="s">
         <v>19</v>
       </c>
@@ -54754,7 +54715,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1158" s="3" t="s">
         <v>19</v>
       </c>
@@ -54801,7 +54762,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1159" s="3" t="s">
         <v>19</v>
       </c>
@@ -54848,7 +54809,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1160" s="3" t="s">
         <v>19</v>
       </c>
@@ -54895,7 +54856,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="1161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1161" s="3" t="s">
         <v>19</v>
       </c>
@@ -54942,7 +54903,7 @@
         <v>0.96099999999999997</v>
       </c>
     </row>
-    <row r="1162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1162" s="3" t="s">
         <v>19</v>
       </c>
@@ -54989,7 +54950,7 @@
         <v>0.96099999999999997</v>
       </c>
     </row>
-    <row r="1163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1163" s="3" t="s">
         <v>15</v>
       </c>
@@ -55030,7 +54991,7 @@
         <v>0.95199999999999996</v>
       </c>
     </row>
-    <row r="1164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1164" s="3" t="s">
         <v>19</v>
       </c>
@@ -55077,7 +55038,7 @@
         <v>0.95199999999999996</v>
       </c>
     </row>
-    <row r="1165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1165" s="3" t="s">
         <v>19</v>
       </c>
@@ -55128,7 +55089,7 @@
   <autoFilter ref="A1:O1165" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="ecoli"/>
+        <filter val="wdbc"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O161">
